--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run1/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run1/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="513">
   <si>
     <t>Filename</t>
   </si>
@@ -808,745 +808,751 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9727,0.0072,0.0044,0.0006</t>
-  </si>
-  <si>
-    <t>0.0276,0.0085,0.0001,0.9733</t>
-  </si>
-  <si>
-    <t>0.9980,0.0002,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.1328,0.0020,0.0002,0.8902</t>
-  </si>
-  <si>
-    <t>0.9991,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9937,0.0094,0.0003,0.0000</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.9853,0.0019,0.0052,0.0004</t>
+  </si>
+  <si>
+    <t>0.0266,0.0005,0.0001,0.9881</t>
+  </si>
+  <si>
+    <t>0.9901,0.0023,0.0011,0.0007</t>
+  </si>
+  <si>
+    <t>0.0882,0.0015,0.0001,0.9391</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0006,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0008,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0010,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0006,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.8871,0.0055,0.1183,0.0005</t>
+  </si>
+  <si>
+    <t>0.0603,0.0053,0.9392,0.0016</t>
+  </si>
+  <si>
+    <t>0.0368,0.0010,0.9749,0.0001</t>
+  </si>
+  <si>
+    <t>0.0036,0.0017,0.9940,0.0014</t>
+  </si>
+  <si>
+    <t>0.8301,0.0005,0.3043,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9985,0.0021,0.0000</t>
+  </si>
+  <si>
+    <t>0.0790,0.9284,0.0060,0.0007</t>
+  </si>
+  <si>
+    <t>0.0005,0.9987,0.0020,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.8475,0.0004,0.2466,0.0004</t>
+  </si>
+  <si>
+    <t>0.1330,0.0004,0.9297,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.0003,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.0025,0.0020,0.9964,0.0001</t>
+  </si>
+  <si>
+    <t>0.0047,0.0003,0.9960,0.0003</t>
+  </si>
+  <si>
+    <t>0.0092,0.0007,0.9910,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.5383,0.4590,0.0090,0.0002</t>
+  </si>
+  <si>
+    <t>0.8929,0.0709,0.0145,0.0007</t>
+  </si>
+  <si>
+    <t>0.0001,0.0010,0.9998,0.0005</t>
+  </si>
+  <si>
+    <t>0.0080,0.8764,0.2410,0.0001</t>
+  </si>
+  <si>
+    <t>0.9752,0.0113,0.0037,0.0003</t>
+  </si>
+  <si>
+    <t>0.4834,0.0122,0.5214,0.0026</t>
+  </si>
+  <si>
+    <t>0.7541,0.2154,0.0226,0.0008</t>
+  </si>
+  <si>
+    <t>0.0059,0.9561,0.1407,0.0001</t>
+  </si>
+  <si>
+    <t>0.0030,0.6663,0.8130,0.0009</t>
+  </si>
+  <si>
+    <t>0.0022,0.0009,0.9961,0.0003</t>
+  </si>
+  <si>
+    <t>0.0017,0.2826,0.9769,0.0002</t>
+  </si>
+  <si>
+    <t>0.1270,0.0001,0.8877,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.6358,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.9953,0.0107,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0312,0.0146,0.0126,0.9710</t>
+  </si>
+  <si>
+    <t>0.0003,0.9989,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9977,0.1165,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0023,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0105,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0102,0.9989,0.0000</t>
+  </si>
+  <si>
+    <t>0.0062,0.0009,0.9934,0.0004</t>
+  </si>
+  <si>
+    <t>0.0040,0.0002,0.9973,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.0043,0.9971,0.0002</t>
+  </si>
+  <si>
+    <t>0.0030,0.0034,0.9950,0.0002</t>
+  </si>
+  <si>
+    <t>0.9931,0.0067,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0006,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9985,0.0012,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.0101,0.9981,0.0007</t>
+  </si>
+  <si>
+    <t>0.9989,0.0006,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9953,0.0042,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9976,0.0013,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9976,0.9978,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.4605,0.9977,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.0099,0.9979,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9949,0.9975,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0011,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0146,0.9681,0.0242,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.8810,0.0014,0.1674,0.0005</t>
+  </si>
+  <si>
+    <t>0.4420,0.0093,0.6072,0.0008</t>
+  </si>
+  <si>
+    <t>0.0016,0.0020,0.9983,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.9767,0.9880,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9901,0.9762,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9992,0.7707,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9963,0.9957,0.0000</t>
+  </si>
+  <si>
+    <t>0.0068,0.0001,0.0099,0.9887</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.0015,0.9995</t>
+  </si>
+  <si>
+    <t>0.0017,0.0002,0.0009,0.9985</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9972,0.9653,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9939,0.9859,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9714,0.9617,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9543,0.9965,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9982,0.9910,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9833,0.9879,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0020,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9980,0.0026,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9981,0.0022,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0009,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0008,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0010,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0008,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0100,0.0022,0.9892,0.0001</t>
+  </si>
+  <si>
+    <t>0.9546,0.0005,0.0713,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.0002,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.9982,0.0016,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0045,0.9921,0.0039,0.0000</t>
+  </si>
+  <si>
+    <t>0.0328,0.9579,0.0089,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.9987,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9990,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.5167,0.5300,0.0093,0.0003</t>
+  </si>
+  <si>
+    <t>0.7037,0.0027,0.3372,0.0017</t>
+  </si>
+  <si>
+    <t>0.0607,0.0032,0.9511,0.0003</t>
+  </si>
+  <si>
+    <t>0.8527,0.0233,0.0557,0.0021</t>
+  </si>
+  <si>
+    <t>0.1697,0.0028,0.8513,0.0022</t>
+  </si>
+  <si>
+    <t>0.0970,0.0322,0.0370,0.5284</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0048,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9984,0.0040,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9952,0.9867,0.0000</t>
+  </si>
+  <si>
+    <t>0.0276,0.9526,0.0138,0.0000</t>
+  </si>
+  <si>
+    <t>0.5161,0.3483,0.0422,0.0003</t>
+  </si>
+  <si>
+    <t>0.6283,0.3287,0.0241,0.0004</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9949,0.0028,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9972,0.0019,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0006,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0003,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.8073,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.7309,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.1416,0.9966,0.0000</t>
+  </si>
+  <si>
+    <t>0.0027,0.0208,0.9926,0.0000</t>
+  </si>
+  <si>
+    <t>0.9791,0.0003,0.0274,0.0002</t>
+  </si>
+  <si>
+    <t>0.9408,0.0033,0.0468,0.0011</t>
+  </si>
+  <si>
+    <t>0.0404,0.0004,0.9748,0.0002</t>
+  </si>
+  <si>
+    <t>0.3662,0.0086,0.6951,0.0005</t>
+  </si>
+  <si>
+    <t>0.0712,0.0006,0.0108,0.9475</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.0001,0.9997</t>
+  </si>
+  <si>
+    <t>0.0000,0.9981,0.7586,0.0000</t>
+  </si>
+  <si>
+    <t>0.9965,0.0021,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.5078,0.5425,0.0249,0.0051</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.5356,0.5256,0.0096,0.0009</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.7076,0.0006,0.0030,0.2329</t>
+  </si>
+  <si>
+    <t>0.0016,0.0253,0.9944,0.0014</t>
+  </si>
+  <si>
+    <t>0.9916,0.0005,0.0036,0.0009</t>
+  </si>
+  <si>
+    <t>0.9970,0.0009,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.3965,0.5066,0.0411,0.0005</t>
+  </si>
+  <si>
+    <t>0.9987,0.0001,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.9654,0.0037,0.0184,0.0003</t>
+  </si>
+  <si>
+    <t>0.0457,0.9250,0.0202,0.0021</t>
+  </si>
+  <si>
+    <t>0.9668,0.0032,0.0167,0.0002</t>
+  </si>
+  <si>
+    <t>0.9832,0.0021,0.0060,0.0002</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9981,0.0010,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0001,0.0001</t>
   </si>
   <si>
     <t>0.9997,0.0001,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.9979,0.0020,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9980,0.0018,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.4253,0.0016,0.7105,0.0004</t>
-  </si>
-  <si>
-    <t>0.0130,0.0008,0.9886,0.0002</t>
-  </si>
-  <si>
-    <t>0.3373,0.0012,0.7948,0.0002</t>
-  </si>
-  <si>
-    <t>0.0006,0.0005,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.9746,0.0009,0.0252,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.0270,0.9720,0.0031,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.9989,0.0026,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.7649,0.0038,0.2673,0.0014</t>
-  </si>
-  <si>
-    <t>0.0504,0.0012,0.9631,0.0003</t>
-  </si>
-  <si>
-    <t>0.0048,0.0003,0.9952,0.0001</t>
-  </si>
-  <si>
-    <t>0.0021,0.0007,0.9978,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.0001,0.9986,0.0003</t>
-  </si>
-  <si>
-    <t>0.0026,0.0006,0.9968,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.5917,0.3649,0.0118,0.0004</t>
-  </si>
-  <si>
-    <t>0.8640,0.0607,0.0277,0.0008</t>
-  </si>
-  <si>
-    <t>0.0001,0.0013,0.9997,0.0008</t>
-  </si>
-  <si>
-    <t>0.0114,0.6940,0.5713,0.0002</t>
-  </si>
-  <si>
-    <t>0.9734,0.0088,0.0069,0.0004</t>
-  </si>
-  <si>
-    <t>0.0861,0.0152,0.9054,0.0041</t>
-  </si>
-  <si>
-    <t>0.7205,0.2712,0.0161,0.0007</t>
-  </si>
-  <si>
-    <t>0.0003,0.9810,0.5595,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.6662,0.9365,0.0004</t>
-  </si>
-  <si>
-    <t>0.0016,0.0032,0.9968,0.0004</t>
-  </si>
-  <si>
-    <t>0.0017,0.1247,0.9850,0.0002</t>
-  </si>
-  <si>
-    <t>0.1787,0.0001,0.8384,0.0008</t>
-  </si>
-  <si>
-    <t>0.0002,0.0914,0.9983,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9986,0.0056,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0012,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0925,0.4056,0.0684,0.5618</t>
-  </si>
-  <si>
-    <t>0.0002,0.9990,0.0034,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9987,0.0120,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0034,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0064,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0592,0.9978,0.0000</t>
-  </si>
-  <si>
-    <t>0.0169,0.0005,0.9855,0.0012</t>
-  </si>
-  <si>
-    <t>0.0069,0.0002,0.9955,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.0068,0.9970,0.0002</t>
-  </si>
-  <si>
-    <t>0.0045,0.0007,0.9947,0.0003</t>
-  </si>
-  <si>
-    <t>0.9971,0.0026,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9981,0.0008,0.0005,0.0001</t>
+    <t>0.9457,0.0331,0.0033,0.0005</t>
+  </si>
+  <si>
+    <t>0.8040,0.2386,0.0048,0.0003</t>
+  </si>
+  <si>
+    <t>0.7114,0.3423,0.0076,0.0007</t>
+  </si>
+  <si>
+    <t>0.4755,0.0083,0.5827,0.0007</t>
+  </si>
+  <si>
+    <t>0.9949,0.0043,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9969,0.0008,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9928,0.0050,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.9798,0.0169,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.0044,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.9937,0.0032,0.0024,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0013,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0040,0.9987,0.0002</t>
+  </si>
+  <si>
+    <t>0.0292,0.0020,0.9784,0.0001</t>
+  </si>
+  <si>
+    <t>0.0014,0.0131,0.9963,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0140,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0001,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0047,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0037,0.0038,0.9936,0.0004</t>
+  </si>
+  <si>
+    <t>0.0655,0.0056,0.9367,0.0010</t>
+  </si>
+  <si>
+    <t>0.4336,0.0092,0.6247,0.0011</t>
+  </si>
+  <si>
+    <t>0.2679,0.0191,0.6970,0.0008</t>
+  </si>
+  <si>
+    <t>0.0512,0.2451,0.7211,0.0013</t>
+  </si>
+  <si>
+    <t>0.8868,0.0042,0.1369,0.0007</t>
+  </si>
+  <si>
+    <t>0.7612,0.0008,0.3134,0.0013</t>
+  </si>
+  <si>
+    <t>0.5080,0.0079,0.5197,0.0010</t>
+  </si>
+  <si>
+    <t>0.0720,0.9553,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.0474,0.9663,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.8631,0.1974,0.0021,0.0002</t>
+  </si>
+  <si>
+    <t>0.9910,0.0058,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.4499,0.6585,0.0039,0.0008</t>
+  </si>
+  <si>
+    <t>0.8728,0.0160,0.0665,0.0007</t>
+  </si>
+  <si>
+    <t>0.9898,0.0001,0.0122,0.0001</t>
+  </si>
+  <si>
+    <t>0.7212,0.0273,0.1457,0.0130</t>
+  </si>
+  <si>
+    <t>0.0754,0.0018,0.9395,0.0009</t>
+  </si>
+  <si>
+    <t>0.7831,0.0147,0.1466,0.0032</t>
+  </si>
+  <si>
+    <t>0.0015,0.0007,0.9976,0.0012</t>
+  </si>
+  <si>
+    <t>0.0410,0.0082,0.9413,0.0005</t>
+  </si>
+  <si>
+    <t>0.0007,0.0208,0.9973,0.0001</t>
+  </si>
+  <si>
+    <t>0.0360,0.0060,0.9514,0.0006</t>
+  </si>
+  <si>
+    <t>0.0016,0.1682,0.9747,0.0003</t>
+  </si>
+  <si>
+    <t>0.9993,0.0007,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0010,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9864,0.0139,0.0010,0.0004</t>
+  </si>
+  <si>
+    <t>0.9968,0.0020,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9973,0.0021,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9938,0.0052,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.9980,0.0012,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0006,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0125,0.0035,0.9892,0.0001</t>
+  </si>
+  <si>
+    <t>0.3802,0.0231,0.5665,0.0019</t>
+  </si>
+  <si>
+    <t>0.8579,0.0043,0.1149,0.0031</t>
+  </si>
+  <si>
+    <t>0.0009,0.0006,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0110,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9423,0.9679,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0060,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0138,0.0013,0.9878,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0013,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0089,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0099,0.0016,0.9869,0.0016</t>
+  </si>
+  <si>
+    <t>0.8829,0.0015,0.1358,0.0010</t>
+  </si>
+  <si>
+    <t>0.8231,0.0005,0.2490,0.0008</t>
+  </si>
+  <si>
+    <t>0.9371,0.0013,0.0674,0.0010</t>
+  </si>
+  <si>
+    <t>0.9987,0.0010,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9942,0.0085,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0007,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9851,0.0224,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0014,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0008,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.9991,0.0006,0.0001,0.0001</t>
   </si>
   <si>
-    <t>0.0003,0.0181,0.9994,0.0003</t>
-  </si>
-  <si>
-    <t>0.9990,0.0004,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9937,0.0063,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9938,0.9963,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.5429,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.1485,0.9968,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9976,0.9949,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0010,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.2179,0.7939,0.0113,0.0007</t>
-  </si>
-  <si>
-    <t>0.0004,0.9991,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.6750,0.0025,0.4471,0.0008</t>
-  </si>
-  <si>
-    <t>0.8543,0.0211,0.0750,0.0009</t>
-  </si>
-  <si>
-    <t>0.0008,0.0019,0.9991,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9992,0.9766,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9886,0.9571,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9979,0.7403,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9948,0.9907,0.0000</t>
-  </si>
-  <si>
-    <t>0.0127,0.0001,0.0096,0.9796</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0004,0.0002,0.0005,0.9996</t>
-  </si>
-  <si>
-    <t>0.0013,0.0001,0.0010,0.9988</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0003,0.9998</t>
-  </si>
-  <si>
-    <t>0.0000,0.9929,0.9897,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.8882,0.9896,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9180,0.8576,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9599,0.9931,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9991,0.9962,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9789,0.9833,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0011,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9973,0.0035,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0017,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0005,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0010,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0008,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9967,0.0032,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0131,0.0034,0.9848,0.0002</t>
-  </si>
-  <si>
-    <t>0.9796,0.0002,0.0208,0.0001</t>
-  </si>
-  <si>
-    <t>0.0065,0.0001,0.9957,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.9986,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.0070,0.9907,0.0025,0.0000</t>
-  </si>
-  <si>
-    <t>0.0217,0.9767,0.0037,0.0001</t>
-  </si>
-  <si>
-    <t>0.0106,0.9853,0.0043,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.9979,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.4588,0.6143,0.0072,0.0003</t>
-  </si>
-  <si>
-    <t>0.5692,0.0027,0.4992,0.0014</t>
-  </si>
-  <si>
-    <t>0.2293,0.0051,0.8054,0.0013</t>
-  </si>
-  <si>
-    <t>0.5969,0.0140,0.3455,0.0038</t>
-  </si>
-  <si>
-    <t>0.1833,0.0039,0.8566,0.0012</t>
-  </si>
-  <si>
-    <t>0.0509,0.0681,0.0375,0.6557</t>
-  </si>
-  <si>
-    <t>0.0001,0.9991,0.0063,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0018,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9978,0.9892,0.0000</t>
-  </si>
-  <si>
-    <t>0.0039,0.9923,0.0044,0.0000</t>
-  </si>
-  <si>
-    <t>0.4610,0.4936,0.0247,0.0003</t>
-  </si>
-  <si>
-    <t>0.8641,0.0942,0.0152,0.0004</t>
-  </si>
-  <si>
-    <t>0.9993,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9972,0.0013,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9977,0.0008,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9932,0.0029,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0006,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0006,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.1863,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.3851,0.9978,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0700,0.9974,0.0000</t>
-  </si>
-  <si>
-    <t>0.0041,0.0228,0.9895,0.0001</t>
-  </si>
-  <si>
-    <t>0.9484,0.0019,0.0411,0.0010</t>
-  </si>
-  <si>
-    <t>0.7974,0.0020,0.2558,0.0012</t>
-  </si>
-  <si>
-    <t>0.0624,0.0004,0.9649,0.0002</t>
-  </si>
-  <si>
-    <t>0.8995,0.0044,0.0981,0.0009</t>
-  </si>
-  <si>
-    <t>0.0539,0.0002,0.0022,0.9702</t>
+    <t>0.0026,0.0023,0.9972,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0110,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0098,0.9983,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0182,0.9976,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0029,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0217,0.0003,0.9850,0.0003</t>
+  </si>
+  <si>
+    <t>0.0020,0.0023,0.9970,0.0002</t>
+  </si>
+  <si>
+    <t>0.0073,0.0003,0.9929,0.0002</t>
+  </si>
+  <si>
+    <t>0.9837,0.0018,0.0055,0.0007</t>
+  </si>
+  <si>
+    <t>0.0115,0.0118,0.0001,0.9931</t>
+  </si>
+  <si>
+    <t>0.0200,0.0001,0.0047,0.9842</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.0001,1.0000</t>
   </si>
   <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.0001,0.9997</t>
-  </si>
-  <si>
-    <t>0.0000,0.9976,0.9741,0.0000</t>
-  </si>
-  <si>
-    <t>0.9962,0.0030,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.1660,0.8540,0.0079,0.0124</t>
-  </si>
-  <si>
-    <t>0.4143,0.6393,0.0115,0.0017</t>
-  </si>
-  <si>
-    <t>0.9988,0.0002,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.8744,0.0006,0.0005,0.0935</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0021,0.0136,0.9943,0.0022</t>
-  </si>
-  <si>
-    <t>0.9828,0.0007,0.0072,0.0022</t>
-  </si>
-  <si>
-    <t>0.9972,0.0010,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.2581,0.7194,0.0191,0.0005</t>
-  </si>
-  <si>
-    <t>0.9964,0.0004,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.9899,0.0015,0.0040,0.0002</t>
-  </si>
-  <si>
-    <t>0.6319,0.2422,0.0532,0.0016</t>
-  </si>
-  <si>
-    <t>0.9657,0.0016,0.0364,0.0002</t>
-  </si>
-  <si>
-    <t>0.9893,0.0010,0.0039,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.8882,0.0988,0.0028,0.0006</t>
-  </si>
-  <si>
-    <t>0.6779,0.3559,0.0122,0.0007</t>
-  </si>
-  <si>
-    <t>0.7524,0.2264,0.0178,0.0012</t>
-  </si>
-  <si>
-    <t>0.0709,0.0100,0.9458,0.0003</t>
-  </si>
-  <si>
-    <t>0.9873,0.0122,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9949,0.0021,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.9972,0.0025,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9781,0.0180,0.0015,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.0083,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9521,0.0131,0.0233,0.0006</t>
-  </si>
-  <si>
-    <t>0.0003,0.0010,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0089,0.9986,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.0029,0.9976,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.0377,0.9942,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0097,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0017,0.0001,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0015,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0113,0.0080,0.9820,0.0003</t>
-  </si>
-  <si>
-    <t>0.0223,0.0021,0.9766,0.0004</t>
-  </si>
-  <si>
-    <t>0.1718,0.0058,0.8657,0.0008</t>
-  </si>
-  <si>
-    <t>0.2615,0.0044,0.7957,0.0004</t>
-  </si>
-  <si>
-    <t>0.0426,0.0318,0.9214,0.0005</t>
-  </si>
-  <si>
-    <t>0.4413,0.0045,0.6775,0.0005</t>
-  </si>
-  <si>
-    <t>0.8479,0.0027,0.1529,0.0024</t>
-  </si>
-  <si>
-    <t>0.1907,0.0088,0.8354,0.0005</t>
-  </si>
-  <si>
-    <t>0.6658,0.4737,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.0095,0.9919,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.8592,0.2197,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.9799,0.0157,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.7398,0.3228,0.0042,0.0005</t>
-  </si>
-  <si>
-    <t>0.7963,0.0025,0.2824,0.0003</t>
-  </si>
-  <si>
-    <t>0.9737,0.0003,0.0384,0.0002</t>
-  </si>
-  <si>
-    <t>0.8522,0.0121,0.0626,0.0065</t>
-  </si>
-  <si>
-    <t>0.1873,0.0176,0.8391,0.0010</t>
-  </si>
-  <si>
-    <t>0.3577,0.0018,0.6898,0.0025</t>
-  </si>
-  <si>
-    <t>0.0006,0.0005,0.9990,0.0002</t>
-  </si>
-  <si>
-    <t>0.0533,0.0010,0.9505,0.0006</t>
-  </si>
-  <si>
-    <t>0.0045,0.0081,0.9906,0.0003</t>
-  </si>
-  <si>
-    <t>0.0918,0.0016,0.9298,0.0002</t>
-  </si>
-  <si>
-    <t>0.0014,0.0221,0.9932,0.0002</t>
-  </si>
-  <si>
-    <t>0.9994,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9965,0.0014,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9730,0.0333,0.0012,0.0003</t>
-  </si>
-  <si>
-    <t>0.9974,0.0021,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9967,0.0021,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9944,0.0063,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9947,0.0037,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0094,0.9985,0.0001</t>
-  </si>
-  <si>
-    <t>0.7242,0.0396,0.1642,0.0009</t>
-  </si>
-  <si>
-    <t>0.9049,0.0011,0.0958,0.0013</t>
-  </si>
-  <si>
-    <t>0.0007,0.0001,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0015,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.6722,0.9986,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0009,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0058,0.0007,0.9950,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0058,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0113,0.9977,0.0002</t>
-  </si>
-  <si>
-    <t>0.0020,0.0007,0.9969,0.0012</t>
-  </si>
-  <si>
-    <t>0.8312,0.0027,0.1862,0.0013</t>
-  </si>
-  <si>
-    <t>0.7667,0.0008,0.3339,0.0008</t>
-  </si>
-  <si>
-    <t>0.9304,0.0017,0.0676,0.0010</t>
-  </si>
-  <si>
-    <t>0.9965,0.0029,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9974,0.0025,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0006,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9963,0.0039,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9983,0.0017,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0014,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0877,0.0060,0.9374,0.0009</t>
-  </si>
-  <si>
-    <t>0.0001,0.0060,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0377,0.9965,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.0065,0.9972,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0020,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.1002,0.0019,0.8999,0.0027</t>
-  </si>
-  <si>
-    <t>0.0166,0.0087,0.9796,0.0004</t>
-  </si>
-  <si>
-    <t>0.0010,0.0003,0.9979,0.0005</t>
-  </si>
-  <si>
-    <t>0.9946,0.0008,0.0013,0.0006</t>
-  </si>
-  <si>
-    <t>0.0292,0.0018,0.0005,0.9835</t>
-  </si>
-  <si>
-    <t>0.0128,0.0001,0.0056,0.9890</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.9604,0.0012,0.0216,0.0017</t>
+    <t>0.9466,0.0023,0.0251,0.0026</t>
   </si>
 </sst>
 </file>
@@ -1932,7 +1938,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1946,7 +1952,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1960,7 +1966,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1974,7 +1980,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1988,7 +1994,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2002,7 +2008,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2016,7 +2022,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2030,7 +2036,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2044,7 +2050,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2058,7 +2064,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2072,7 +2078,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2086,7 +2092,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2097,10 +2103,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2114,7 +2120,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2128,7 +2134,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2142,7 +2148,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2156,7 +2162,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2170,7 +2176,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2184,7 +2190,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2198,7 +2204,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2212,7 +2218,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2226,7 +2232,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2240,7 +2246,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2254,7 +2260,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2268,7 +2274,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2282,7 +2288,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2296,7 +2302,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2310,7 +2316,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2324,7 +2330,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2338,7 +2344,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2352,7 +2358,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2366,7 +2372,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2377,10 +2383,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2394,7 +2400,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2408,7 +2414,7 @@
         <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2422,7 +2428,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2433,10 +2439,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2450,7 +2456,7 @@
         <v>263</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2464,7 +2470,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2478,7 +2484,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2492,7 +2498,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2503,10 +2509,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2520,7 +2526,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2534,7 +2540,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2548,7 +2554,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2562,7 +2568,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2576,7 +2582,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2590,7 +2596,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2604,7 +2610,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2618,7 +2624,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2632,7 +2638,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2646,7 +2652,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2660,7 +2666,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2674,7 +2680,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2688,7 +2694,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2702,7 +2708,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2716,7 +2722,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2730,7 +2736,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2744,7 +2750,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2758,7 +2764,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2772,7 +2778,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2786,7 +2792,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2797,10 +2803,10 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2814,7 +2820,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2828,7 +2834,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2842,7 +2848,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2856,7 +2862,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2870,7 +2876,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2884,7 +2890,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2895,10 +2901,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2912,7 +2918,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2926,7 +2932,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2940,7 +2946,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2954,7 +2960,7 @@
         <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2968,7 +2974,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2982,7 +2988,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2996,7 +3002,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3010,7 +3016,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3024,7 +3030,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3038,7 +3044,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3052,7 +3058,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3066,7 +3072,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3080,7 +3086,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3094,7 +3100,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3108,7 +3114,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3122,7 +3128,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3136,7 +3142,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3150,7 +3156,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3164,7 +3170,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3178,7 +3184,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3192,7 +3198,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3206,7 +3212,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3220,7 +3226,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3234,7 +3240,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3248,7 +3254,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3262,7 +3268,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3304,7 +3310,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3360,7 +3366,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3374,7 +3380,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3388,7 +3394,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3402,7 +3408,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3416,7 +3422,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3430,7 +3436,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3444,7 +3450,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3458,7 +3464,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3472,7 +3478,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3486,7 +3492,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3500,7 +3506,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3511,10 +3517,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D115" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3528,7 +3534,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3542,7 +3548,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3556,7 +3562,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3570,7 +3576,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3584,7 +3590,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3598,7 +3604,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3612,7 +3618,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3805,7 +3811,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
         <v>396</v>
@@ -3819,7 +3825,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
         <v>397</v>
@@ -3903,7 +3909,7 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D143" t="s">
         <v>403</v>
@@ -4001,7 +4007,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D150" t="s">
         <v>410</v>
@@ -4018,7 +4024,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>271</v>
+        <v>411</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4029,10 +4035,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D152" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4046,7 +4052,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4060,7 +4066,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4074,7 +4080,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>414</v>
+        <v>388</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4169,7 +4175,7 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
         <v>421</v>
@@ -4214,7 +4220,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4228,7 +4234,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>274</v>
+        <v>424</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4242,7 +4248,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4256,7 +4262,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4270,7 +4276,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4284,7 +4290,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4298,7 +4304,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>274</v>
+        <v>429</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4312,7 +4318,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>428</v>
+        <v>389</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4326,7 +4332,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4340,7 +4346,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4354,7 +4360,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4368,7 +4374,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4382,7 +4388,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4396,7 +4402,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4410,7 +4416,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4424,7 +4430,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4438,7 +4444,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4452,7 +4458,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4466,7 +4472,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4480,7 +4486,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4494,7 +4500,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4508,7 +4514,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4522,7 +4528,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4536,7 +4542,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4550,7 +4556,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4564,7 +4570,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4578,7 +4584,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4592,7 +4598,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4606,7 +4612,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4620,7 +4626,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4631,10 +4637,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4648,7 +4654,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4659,10 +4665,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D197" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4673,10 +4679,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4690,7 +4696,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4704,7 +4710,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4718,7 +4724,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4729,10 +4735,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4746,7 +4752,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4760,7 +4766,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4774,7 +4780,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4788,7 +4794,7 @@
         <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4799,10 +4805,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4816,7 +4822,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4830,7 +4836,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4844,7 +4850,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4858,7 +4864,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4872,7 +4878,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4886,7 +4892,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4900,7 +4906,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4914,7 +4920,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4928,7 +4934,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4942,7 +4948,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4956,7 +4962,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4970,7 +4976,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4984,7 +4990,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4998,7 +5004,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5009,10 +5015,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5026,7 +5032,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5040,7 +5046,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5054,7 +5060,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5068,7 +5074,7 @@
         <v>263</v>
       </c>
       <c r="D226" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5082,7 +5088,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5096,7 +5102,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5110,7 +5116,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5124,7 +5130,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5138,7 +5144,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5152,7 +5158,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5166,7 +5172,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5180,7 +5186,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5194,7 +5200,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5208,7 +5214,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5222,7 +5228,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5236,7 +5242,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5250,7 +5256,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>274</v>
+        <v>496</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5264,7 +5270,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5278,7 +5284,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5292,7 +5298,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5306,7 +5312,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5320,7 +5326,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5334,7 +5340,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5348,7 +5354,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5362,7 +5368,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5376,7 +5382,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5390,7 +5396,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5404,7 +5410,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5418,7 +5424,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5432,7 +5438,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5446,7 +5452,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5460,7 +5466,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>405</v>
+        <v>511</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5474,7 +5480,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>509</v>
+        <v>341</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5488,7 +5494,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
   </sheetData>
